--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambohidrony.xlsx
@@ -420,12 +420,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,12 +506,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,12 +523,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -581,12 +563,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -627,12 +603,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -650,12 +620,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -788,12 +752,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -903,12 +861,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -971,12 +923,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <v>0.2</v>
       </c>
     </row>
     <row r="28">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_ambohidrony.xlsx
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>45</v>
-      </c>
-      <c r="E2">
-        <v>52.3</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,8 +411,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -434,14 +434,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>8.1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -457,14 +457,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>18.6</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="6">
@@ -480,14 +480,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>12.8</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -503,8 +497,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>23.4</v>
       </c>
     </row>
     <row r="8">
@@ -520,8 +520,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>10.6</v>
       </c>
     </row>
     <row r="9">
@@ -537,14 +543,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>39</v>
-      </c>
-      <c r="E9">
-        <v>65</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -560,8 +560,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>39.3</v>
       </c>
     </row>
     <row r="11">
@@ -577,14 +583,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>11</v>
-      </c>
-      <c r="E11">
-        <v>18.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -617,31 +617,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>405</v>
-      </c>
-      <c r="E14">
-        <v>46.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -657,14 +651,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D15">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -680,14 +674,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D16">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E16">
-        <v>7.1</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="17">
@@ -703,14 +697,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D17">
         <v>289</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="18">
@@ -726,14 +720,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D18">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E18">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -749,8 +743,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -766,14 +766,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D20">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E20">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="21">
@@ -789,14 +789,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D21">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -812,14 +812,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D22">
-        <v>418</v>
+        <v>11</v>
       </c>
       <c r="E22">
-        <v>71.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="23">
@@ -835,14 +835,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>19</v>
-      </c>
-      <c r="E23">
-        <v>3.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -858,8 +852,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>101</v>
+      </c>
+      <c r="E24">
+        <v>47.6</v>
       </c>
     </row>
     <row r="25">
@@ -875,14 +875,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D25">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="E25">
-        <v>17.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="26">
@@ -898,14 +898,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E26">
-        <v>3.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="27">
@@ -921,8 +921,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>19</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -938,14 +944,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D28">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E28">
-        <v>4.3</v>
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
